--- a/src/app/modules/dashboard/excel_files/whole-food-plant-based-diet-pizza-recipes.xlsx
+++ b/src/app/modules/dashboard/excel_files/whole-food-plant-based-diet-pizza-recipes.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pizza', 'flatbread']</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
